--- a/Output/Excel_Dashboard_Template.xlsx
+++ b/Output/Excel_Dashboard_Template.xlsx
@@ -9,12 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Incoming trains" sheetId="1" r:id="rId1"/>
     <sheet name="Wagon groups" sheetId="2" r:id="rId2"/>
-    <sheet name="Outgoing trains" sheetId="3" r:id="rId3"/>
+    <sheet name="Outbound trains" sheetId="3" r:id="rId3"/>
     <sheet name="Workers" sheetId="4" r:id="rId4"/>
     <sheet name="Shunting Locomotives" sheetId="5" r:id="rId5"/>
   </sheets>
